--- a/peptide_Supplementary Information.xlsx
+++ b/peptide_Supplementary Information.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KKU\PhD\papers\11.Generative_ACPs\SI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10D8D2AE-2C73-42EE-9C69-CE20C1DD3AD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A6A7658-0226-4EB3-A7FF-24B1EBC4BF78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3218,6 +3218,105 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Dataset used for developing predictive models for the colon endpoint (n = 360)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Graduate School in the Program of Research and Development in Pharmaceuticals, Faculty of Pharmaceutical Sciences, Khon Kaen University, Khon Kaen, 40002, Thailand.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>c</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Division of Pharmaceutical Chemistry, Faculty of Pharmaceutical Sciences, Khon Kaen University, Khon Kaen, 40002, Thailand.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Department of Pharmacology, Faculty of Medicine, Khon Kaen University, Khon Kaen, 40002, Thailand.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">*Corresponding author. E mail: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tarasri@kku.ac.th</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>b</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Faculty of Health Sciences, College of Natural Sciences, Can Tho University, Can Tho, 900000, Vietnam.</t>
     </r>
   </si>
   <si>
@@ -3285,7 +3384,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>, Kim Leang Set</t>
+      <t>, Kimleang Set</t>
     </r>
     <r>
       <rPr>
@@ -3360,105 +3459,6 @@
         <scheme val="minor"/>
       </rPr>
       <t>c,∗</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>a</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Graduate School in the Program of Research and Development in Pharmaceuticals, Faculty of Pharmaceutical Sciences, Khon Kaen University, Khon Kaen, 40002, Thailand.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>c</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Division of Pharmaceutical Chemistry, Faculty of Pharmaceutical Sciences, Khon Kaen University, Khon Kaen, 40002, Thailand.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>d</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Department of Pharmacology, Faculty of Medicine, Khon Kaen University, Khon Kaen, 40002, Thailand.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">*Corresponding author. E mail: </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>tarasri@kku.ac.th</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>b</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Faculty of Health Sciences, College of Natural Sciences, Can Tho University, Can Tho, 900000, Vietnam.</t>
     </r>
   </si>
 </sst>
@@ -3893,33 +3893,33 @@
     </row>
     <row r="4" spans="1:1" s="14" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
-        <v>1043</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="5" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="6" spans="1:1" s="14" customFormat="1" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="7" spans="1:1" s="14" customFormat="1" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="8" spans="1:1" s="14" customFormat="1" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="9" spans="1:1" s="14" customFormat="1" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="10" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="18" x14ac:dyDescent="0.35">

--- a/peptide_Supplementary Information.xlsx
+++ b/peptide_Supplementary Information.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KKU\PhD\papers\11.Generative_ACPs\SI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A6A7658-0226-4EB3-A7FF-24B1EBC4BF78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA2AC13F-4F0E-4CF5-AEFF-331690F76D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3343,27 +3343,6 @@
         <scheme val="minor"/>
       </rPr>
       <t>, Sastiya Kampaengsri</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>c</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, Nachapapon Lunda</t>
     </r>
     <r>
       <rPr>
